--- a/docs/Web pages.xlsx
+++ b/docs/Web pages.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Pegboard.Web\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E27FCCB4-7979-4742-B03E-8840F9FA9C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F23DD58-2D36-4A9F-9CC7-EE0A614773E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-9750" windowWidth="38620" windowHeight="21100" xr2:uid="{DA042D2E-F3BD-4BD6-B120-4D79492D7016}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DA042D2E-F3BD-4BD6-B120-4D79492D7016}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="70">
   <si>
     <t>Page</t>
   </si>
@@ -230,45 +230,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Single page to avoid friction for users, grouped into sections
-Core Matchmaking &amp; Fairness
-• Smart court assignments
-• Balanced player rotation
-• Fairness tracking (who's played/waited)
-• Competitive matchups based on skill
-• High performance
-✅ Session Management
-• Add/remove players on the fly
-• Handle late arrivals or early leavers
-• Pause/resume sessions
-• Manage an unlimited number of courts
-✅ Customization &amp; Control
-• Control match duration
-• Gender, pairing, or level filters
-• Court priority/rules
-• Optional manual overrides
-✅ Post-Session &amp; Reporting
-• Export match history
-• See player participation summaries
-• Use data for league pairing decisions
-✅ Other Helpful Tools
-• Session cheat sheet
-• Offline support
-• One-time license model (no subscription) 
-🎮 Flexible Club Night Modes
-• 🔄 Fully Automatic Mode
-• Courts auto-fill based on fairness, rest time, and match quality
-• Great for clubs wanting smoother nights and less admin effort
-• Minimal manual interaction — just add players and let it run
-• 🤝 Manual Picker Mode with Auto Assist
-• Keep your tradition: first player in queue picks from next 7
-• Use ePegboard’s “Auto Pick” to recommend smart pairings
-• Still tracks fairness and rest to guide better decisions
-• Clubs can switch between modes or mix styles during a session.
-“Not sure which style fits your club? Try both in the free trial — switch anytime.”
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">organise into sections.
 General Questions
 What is ePegboard?
@@ -315,6 +276,75 @@
   </si>
   <si>
     <t>Drafting</t>
+  </si>
+  <si>
+    <t>• Smart court assignments
+• Balanced player rotation
+• Fairness tracking (who's played/waited)
+• Competitive matchups based on skill
+• High performance</t>
+  </si>
+  <si>
+    <t>Core matchmaking and fairness</t>
+  </si>
+  <si>
+    <t>Session Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Add/remove players on the fly
+• Handle late arrivals or early leavers
+• Pause/resume sessions
+• Manage an unlimited number of courts
+</t>
+  </si>
+  <si>
+    <t>Customization and control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+• Control match duration
+• Gender, pairing, or level filters
+• Court priority/rules
+• Optional manual overrides
+</t>
+  </si>
+  <si>
+    <t>Post session and reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Export match history
+• See player participation summaries
+• Use data for league pairing decisions
+</t>
+  </si>
+  <si>
+    <t>• 🔄 Fully Automatic Mode
+• Courts auto-fill based on fairness, rest time, and match quality
+• Great for clubs wanting smoother nights and less admin effort
+• Minimal manual interaction — just add players and let it run
+• 🤝 Manual Picker Mode with Auto Assist
+• Keep your tradition: first player in queue picks from next 7
+• Use ePegboard’s “Auto Pick” to recommend smart pairings
+• Still tracks fairness and rest to guide better decisions
+• Clubs can switch between modes or mix styles during a session.
+“Not sure which style fits your club? Try both in the free trial — switch anytime.”</t>
+  </si>
+  <si>
+    <t>Flexible Club Night Modes</t>
+  </si>
+  <si>
+    <t>Other Helpful Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Session cheat sheet
+• Offline support
+• One-time license model (no subscription) </t>
+  </si>
+  <si>
+    <t>Single page to avoid friction for users, grouped into sections</t>
+  </si>
+  <si>
+    <t>suggest change to includce 4. Enter score.   5. view stats … not really a step</t>
   </si>
 </sst>
 </file>
@@ -819,14 +849,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -840,14 +864,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1205,37 +1231,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFACC0AD-89C3-4CE7-B047-163CC4C40979}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="94.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="94.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="81.140625" customWidth="1"/>
     <col min="6" max="6" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1253,7 +1279,7 @@
         <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1270,7 +1296,7 @@
         <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.25">
@@ -1287,7 +1313,7 @@
         <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="300" x14ac:dyDescent="0.25">
@@ -1303,8 +1329,11 @@
       <c r="D5" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="E5" t="s">
+        <v>69</v>
+      </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1321,7 +1350,7 @@
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1336,7 +1365,7 @@
       </c>
       <c r="D7" s="2"/>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="150" x14ac:dyDescent="0.25">
@@ -1346,360 +1375,415 @@
       <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="315.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="5" t="s">
-        <v>48</v>
+      <c r="D9" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="F9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="D16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="2"/>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="F17" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="2"/>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+      <c r="D24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B25" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="1" t="s">
+      <c r="C25" s="2"/>
+      <c r="D25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="F25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="D20"/>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22"/>
-      <c r="F22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="1"/>
-      <c r="F23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25"/>
-      <c r="F25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D26"/>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D27" s="1"/>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>52</v>
+      <c r="B28" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D28"/>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="2"/>
-      <c r="D29" t="s">
-        <v>54</v>
-      </c>
+      <c r="A29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1"/>
       <c r="F29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30"/>
+      <c r="A30" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="2"/>
+      <c r="A31" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="D31"/>
       <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="11"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="D32"/>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="F33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34"/>
+      <c r="F34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36"/>
+      <c r="F36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37"/>
+      <c r="F37" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="7"/>
+      <c r="D38"/>
+      <c r="F38" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="C21:C23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Web pages.xlsx
+++ b/docs/Web pages.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repos\Pegboard.Web\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F23DD58-2D36-4A9F-9CC7-EE0A614773E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96F9B4B-BC48-4B2A-80DB-0B6CB46ABDCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DA042D2E-F3BD-4BD6-B120-4D79492D7016}"/>
+    <workbookView xWindow="-38510" yWindow="-9750" windowWidth="38620" windowHeight="21100" xr2:uid="{DA042D2E-F3BD-4BD6-B120-4D79492D7016}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
